--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T13:15:57+00:00</t>
+    <t>2026-09-14T12:52:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:52:13+00:00</t>
+    <t>2026-09-14T13:01:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:01:52+00:00</t>
+    <t>2026-09-14T13:11:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,25 +105,10 @@
     <t>BooleanType[false]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.3.1937.777.24.5.2.3</t>
-  </si>
-  <si>
-    <t>unbekannt</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.3.1937.777.24.5.2.2</t>
-  </si>
-  <si>
-    <t>nicht gültig</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.3.1937.777.24.5.2.1</t>
-  </si>
-  <si>
-    <t>gültig</t>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
   </si>
   <si>
     <t/>
@@ -404,7 +389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -415,48 +400,26 @@
       <c r="A1" t="s" s="1">
         <v>30</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>24</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>32</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:11:56+00:00</t>
+    <t>2026-09-14T13:21:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
